--- a/output/pdf_financials_xlsx/GGI.xlsx
+++ b/output/pdf_financials_xlsx/GGI.xlsx
@@ -1118,31 +1118,31 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000168</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.171466</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.151264</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.038284</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.025309</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.001217</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.007396</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.006778</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.003358</v>
       </c>
     </row>
     <row r="13">
@@ -2111,31 +2111,31 @@
         <v>-0.436292</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.128399</v>
+        <v>-2.128567</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.062337</v>
+        <v>-0.109129</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.606487</v>
+        <v>-5.757751</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.137459</v>
+        <v>-3.175743</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.033344</v>
+        <v>-2.058653</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.92074</v>
+        <v>-2.921957</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.382033</v>
+        <v>-1.389429</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-31.352356</v>
+        <v>-31.359134</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-1.254289</v>
+        <v>-1.257647</v>
       </c>
     </row>
     <row r="28">
@@ -2233,31 +2233,31 @@
         <v>-0.435146</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.116813</v>
+        <v>-2.116981</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.068703</v>
+        <v>-0.102763</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.60176</v>
+        <v>-5.753024</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.133933</v>
+        <v>-3.172217</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.030702</v>
+        <v>-2.056011</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.918752</v>
+        <v>-2.919969</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.381143</v>
+        <v>-1.388539</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-31.351646</v>
+        <v>-31.358424</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-1.25372</v>
+        <v>-1.257078</v>
       </c>
     </row>
     <row r="30">
@@ -2529,31 +2529,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.026481</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.336848</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.866239</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.024794</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.976944</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.464858</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.191751</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.449571</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.089563</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>14.556042</v>
@@ -2568,19 +2568,19 @@
         <v>0.258145</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.563953</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.088001</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.122106</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.012991</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.355774</v>
       </c>
     </row>
     <row r="35">
@@ -2651,31 +2651,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.026481</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>3.568</v>
+        <v>3.904848</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>10.228082</v>
+        <v>11.094321</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>9.0207</v>
+        <v>10.045494</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.783955</v>
+        <v>6.760899</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.081573</v>
+        <v>2.546431</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.723302</v>
+        <v>1.915053</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.07826900000000001</v>
+        <v>0.52784</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.009127</v>
+        <v>0.09869</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>14.561986</v>
@@ -2690,19 +2690,19 @@
         <v>0.258145</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.563953</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>2.088001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.122106</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.00675</v>
+        <v>0.019741</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.0355</v>
+        <v>0.391274</v>
       </c>
     </row>
     <row r="37">
@@ -3383,31 +3383,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.132676</v>
+        <v>0.106195</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.597492</v>
+        <v>0.260644</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.239318</v>
+        <v>0.373079</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.46687</v>
+        <v>0.442076</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.158788</v>
+        <v>0.181844</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.618319</v>
+        <v>0.153461</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.334689</v>
+        <v>0.142938</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.512633</v>
+        <v>0.06306200000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.143385</v>
+        <v>0.053822</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.02064</v>
@@ -3422,19 +3422,19 @@
         <v>3.174918</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.730943</v>
+        <v>0.16699</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.268082</v>
+        <v>0.180081</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.144111</v>
+        <v>0.022005</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.018153</v>
+        <v>0.005162</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.385224</v>
+        <v>0.02945</v>
       </c>
     </row>
     <row r="49">
@@ -8098,16 +8098,16 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.054054</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.055031</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052745</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.057145</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -8159,16 +8159,16 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.054054</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.055031</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052745</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.057145</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9454,7 +9454,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -10712,7 +10716,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -12282,7 +12290,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -15244,7 +15256,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -19202,7 +19218,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -25298,7 +25314,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -26946,7 +26966,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -29046,7 +29070,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -39762,7 +39790,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">

--- a/output/pdf_financials_xlsx/GGI.xlsx
+++ b/output/pdf_financials_xlsx/GGI.xlsx
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.132062</v>
+        <v>0.336322</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.16128</v>
+        <v>0.45495</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.524838</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.160016</v>
+        <v>0.364276</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.183452</v>
+        <v>0.477122</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.990247</v>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.179321</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0.123715</v>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>0</v>
+        <v>0.034012</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0.034012</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.034012</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0.034012</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.256812</v>
+        <v>0.2228</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -5386,10 +5386,8 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.006143244598380779</v>
       </c>
       <c r="C80" s="3" t="n">
         <v>0.002627109964310172</v>
@@ -5919,7 +5917,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>13.625829</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>14.643817</v>
@@ -6163,7 +6161,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.755635</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>2.02266</v>
@@ -19322,7 +19320,11 @@
           <t>Marketable securities – Note 4</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -19426,7 +19428,11 @@
           <t>Sales taxes receivable – Note 9</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>TaxesReceivable</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -19742,7 +19748,11 @@
           <t>Equipment – Note 6</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -20368,7 +20378,11 @@
           <t>Loan payable – Note 8</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -20576,7 +20590,11 @@
           <t>Share capital – Note 10</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -20680,7 +20698,11 @@
           <t>Contributed surplus – Note 11</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -20890,7 +20912,11 @@
           <t>Sales taxes receivable – Note 10</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>TaxesReceivable</t>
+        </is>
+      </c>
       <c r="E118" s="5" t="n">
         <v>0.09285</v>
       </c>
@@ -20994,7 +21020,11 @@
           <t>Equipment – Note 7</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
         <v>0.179321</v>
       </c>
@@ -21624,7 +21654,11 @@
           <t>Loan payable – Note 9</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>0.034012</v>
       </c>
@@ -21834,7 +21868,11 @@
           <t>Share capital – Note 11</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E127" s="5" t="n">
         <v>13.625829</v>
       </c>
@@ -21938,7 +21976,11 @@
           <t>Contributed surplus – Note 12</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="n">
         <v>1.755635</v>
       </c>
@@ -57492,7 +57534,11 @@
           <t>Consulting fees – Note 15</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -57810,7 +57856,11 @@
           <t>Management fees – Note 15</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -58020,7 +58070,11 @@
           <t>Professional fees – Note 15</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -62138,7 +62192,11 @@
           <t>Consulting fees – Note 16</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E517" s="5" t="n">
         <v>0.04826</v>
       </c>
@@ -62350,7 +62408,11 @@
           <t>Management fees – Note 16</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E519" s="5" t="n">
         <v>0.156</v>
       </c>
@@ -62454,7 +62516,11 @@
           <t>Professional fees – Note 16</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E520" s="5" t="n">
         <v>0.152561</v>
       </c>

--- a/output/pdf_financials_xlsx/GGI.xlsx
+++ b/output/pdf_financials_xlsx/GGI.xlsx
@@ -1405,7 +1405,7 @@
         <v>0.02326</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.034104</v>
+        <v>-1.146832</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1432,7 +1432,7 @@
         <v>2.489272</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.924073</v>
+        <v>0.295</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0.182</v>
@@ -1444,7 +1444,7 @@
         <v>-0.625</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>3.012</v>
+        <v>-3.012</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>-0</v>
@@ -1650,8 +1650,10 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-0.741999</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>5.801397</v>
@@ -1712,7 +1714,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.203476</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -2373,7 +2375,7 @@
         <v>0.3549558304318314</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.4415076767367373</v>
+        <v>-14.84679603352527</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -2400,7 +2402,7 @@
         <v>-44.39985324143264</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-29.45291077907313</v>
+        <v>-9.402513307743623</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-8.950772717257877</v>
@@ -4426,31 +4428,31 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.172377</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.238516</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.292224</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.295739</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.254185</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.195304</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>1.01203</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>1.639069</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>1.853633</v>
       </c>
     </row>
     <row r="65">
@@ -4670,16 +4672,16 @@
         <v>0.855125</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.8826310000000001</v>
+        <v>1.055008</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.26822</v>
+        <v>0.506736</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.513034</v>
+        <v>0.805258</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.3778</v>
+        <v>0.673539</v>
       </c>
       <c r="O68" s="3" t="n">
         <v>0.555765</v>
@@ -5097,16 +5099,16 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.199063</v>
+        <v>0.026686</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.125386</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.044239</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.383827</v>
+        <v>0.088088</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0.054003</v>
@@ -6536,7 +6538,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-0.538523</v>
+        <v>-0.741999</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>6.152768</v>
@@ -7268,13 +7270,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.028158</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.059804</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7292,16 +7294,16 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000323</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.067619</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.08586199999999999</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.101068</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -7515,34 +7517,34 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.175124</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.952413</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.678136</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>2.159024</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>1.583699</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>1.238606</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.45724</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.212645</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.00642</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -8729,13 +8731,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.028158</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.059804</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8753,16 +8755,16 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000323</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.067619</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.08586199999999999</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.101068</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -8800,7 +8802,7 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.121896</v>
+        <v>-1.1817</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.093411</v>
@@ -8818,16 +8820,16 @@
         <v>-0.597201</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.284729</v>
+        <v>-0.285052</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.152211</v>
+        <v>-1.21983</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.110784</v>
+        <v>-1.196646</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.74471</v>
+        <v>-0.845778</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-0.734712</v>
@@ -22756,7 +22758,11 @@
           <t>Deferred income taxes recovery</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23728,7 +23734,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -26476,7 +26486,11 @@
           <t>Deferred income taxes expense (recovery)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -29850,7 +29864,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -30042,7 +30060,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -30838,7 +30860,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -31528,7 +31554,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -32058,7 +32088,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -33734,7 +33768,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -34154,7 +34192,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -35212,7 +35254,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -36902,11 +36948,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" s="5" t="n">
         <v>-0.538523</v>
       </c>
@@ -37648,7 +37690,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -37754,7 +37800,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E281" s="5" t="n">
         <v>-0.028158</v>
       </c>
@@ -40708,7 +40758,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -45154,7 +45208,11 @@
           <t>Deferred income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -54674,7 +54732,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -57004,7 +57066,11 @@
           <t>Deferred income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -63150,7 +63216,11 @@
           <t>Loss from discontinued operations – Note 6</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E526" s="5" t="n">
         <v>-0.203476</v>
       </c>
